--- a/Uncertainty/Uncertainty.xlsx
+++ b/Uncertainty/Uncertainty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Uncertainty/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{467FBAE8-425D-416A-B12A-0FB23595CBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1CC7405-0B1F-404B-90D0-D5A04CB61755}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{467FBAE8-425D-416A-B12A-0FB23595CBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36A55683-C632-415D-A697-72667D50FBC6}"/>
   <bookViews>
-    <workbookView xWindow="6345" yWindow="1125" windowWidth="21570" windowHeight="11295" xr2:uid="{047F7863-0148-4A53-86D1-5BE3CF07051F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{047F7863-0148-4A53-86D1-5BE3CF07051F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -457,7 +457,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -468,7 +468,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -479,7 +479,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
@@ -490,7 +490,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>

--- a/Uncertainty/Uncertainty.xlsx
+++ b/Uncertainty/Uncertainty.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Uncertainty/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Uncertainty/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{467FBAE8-425D-416A-B12A-0FB23595CBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1CC7405-0B1F-404B-90D0-D5A04CB61755}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{467FBAE8-425D-416A-B12A-0FB23595CBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D227DA1-74BF-4BD6-AE52-E64D6CE80D8C}"/>
   <bookViews>
-    <workbookView xWindow="6345" yWindow="1125" windowWidth="21570" windowHeight="11295" xr2:uid="{047F7863-0148-4A53-86D1-5BE3CF07051F}"/>
+    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{047F7863-0148-4A53-86D1-5BE3CF07051F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -468,7 +468,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -479,7 +479,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
@@ -490,7 +490,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>

--- a/Uncertainty/Uncertainty.xlsx
+++ b/Uncertainty/Uncertainty.xlsx
@@ -1,25 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Uncertainty/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{467FBAE8-425D-416A-B12A-0FB23595CBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36A55683-C632-415D-A697-72667D50FBC6}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{467FBAE8-425D-416A-B12A-0FB23595CBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A54A9B14-33AE-4692-B736-F7D411E01971}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{047F7863-0148-4A53-86D1-5BE3CF07051F}"/>
+    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{047F7863-0148-4A53-86D1-5BE3CF07051F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="UNC_Batt_Cap">Sheet1!$B$6</definedName>
+    <definedName name="UNC_Batt_Cost">Sheet1!$B$12</definedName>
+    <definedName name="UNC_Compliance_Fixed">Sheet1!$B$11</definedName>
+    <definedName name="UNC_Cont_Cost">Sheet1!$B$8</definedName>
     <definedName name="UNC_Fluid_C">Sheet1!$B$5</definedName>
     <definedName name="UNC_Fluid_Fill">Sheet1!$B$3</definedName>
     <definedName name="UNC_Fluid_Temp">Sheet1!$B$4</definedName>
+    <definedName name="UNC_Heat_Elem_Tol">Sheet1!$B$9</definedName>
+    <definedName name="UNC_Lid_Mat_Cost">Sheet1!$B$7</definedName>
+    <definedName name="UNC_MFG_Fixed">Sheet1!$B$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t xml:space="preserve">Uncertainty </t>
   </si>
@@ -69,6 +75,36 @@
   </si>
   <si>
     <t>% battery charge</t>
+  </si>
+  <si>
+    <t>UNC_Lid_Mat_Cost</t>
+  </si>
+  <si>
+    <t>% market fluctuations</t>
+  </si>
+  <si>
+    <t>UNC_Cont_Cost</t>
+  </si>
+  <si>
+    <t>UNC_Heat_Elem_Tol</t>
+  </si>
+  <si>
+    <t>% fluctuation in power output</t>
+  </si>
+  <si>
+    <t>% fluctuation in fixed costs</t>
+  </si>
+  <si>
+    <t>UNC_Batt_Cost</t>
+  </si>
+  <si>
+    <t>% fluctuation in batt cost</t>
+  </si>
+  <si>
+    <t>UNC_MFG_Fixed</t>
+  </si>
+  <si>
+    <t>UNC_Compliance_Fixed</t>
   </si>
 </sst>
 </file>
@@ -121,6 +157,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -440,10 +480,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44B3C3DD-FED1-45CC-A2B4-7AA1DDFCB63D}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" customWidth="1"/>
     <col min="3" max="3" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -457,7 +497,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -468,7 +508,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -479,7 +519,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
@@ -490,10 +530,76 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
+        <v>1.05</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Uncertainty/Uncertainty.xlsx
+++ b/Uncertainty/Uncertainty.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Uncertainty/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{467FBAE8-425D-416A-B12A-0FB23595CBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A54A9B14-33AE-4692-B736-F7D411E01971}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="8_{467FBAE8-425D-416A-B12A-0FB23595CBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E3BC2C3-E625-4ACC-A756-37B3C31ACF61}"/>
   <bookViews>
-    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{047F7863-0148-4A53-86D1-5BE3CF07051F}"/>
+    <workbookView xWindow="6255" yWindow="420" windowWidth="21570" windowHeight="11295" xr2:uid="{047F7863-0148-4A53-86D1-5BE3CF07051F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
     <definedName name="UNC_Batt_Cost">Sheet1!$B$12</definedName>
     <definedName name="UNC_Compliance_Fixed">Sheet1!$B$11</definedName>
     <definedName name="UNC_Cont_Cost">Sheet1!$B$8</definedName>
+    <definedName name="UNC_Demand_Variation">Sheet1!$B$15</definedName>
     <definedName name="UNC_Fluid_C">Sheet1!$B$5</definedName>
     <definedName name="UNC_Fluid_Fill">Sheet1!$B$3</definedName>
     <definedName name="UNC_Fluid_Temp">Sheet1!$B$4</definedName>
+    <definedName name="UNC_Heat_Elem_Cost">Sheet1!$B$13</definedName>
     <definedName name="UNC_Heat_Elem_Tol">Sheet1!$B$9</definedName>
     <definedName name="UNC_Lid_Mat_Cost">Sheet1!$B$7</definedName>
     <definedName name="UNC_MFG_Fixed">Sheet1!$B$10</definedName>
+    <definedName name="UNC_Testing_Fixed">Sheet1!$B$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t xml:space="preserve">Uncertainty </t>
   </si>
@@ -105,6 +108,21 @@
   </si>
   <si>
     <t>UNC_Compliance_Fixed</t>
+  </si>
+  <si>
+    <t>UNC_Heat_Elem_Cost</t>
+  </si>
+  <si>
+    <t>% fluctuation</t>
+  </si>
+  <si>
+    <t>% fluctuation heating element cost</t>
+  </si>
+  <si>
+    <t>UNC_Testing_Fixed</t>
+  </si>
+  <si>
+    <t>UNC_Demand_Variation</t>
   </si>
 </sst>
 </file>
@@ -480,10 +498,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44B3C3DD-FED1-45CC-A2B4-7AA1DDFCB63D}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
     <col min="3" max="3" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -602,6 +620,39 @@
         <v>16</v>
       </c>
     </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
